--- a/viaje/CALENDARIO ROMA definitivo.xlsx
+++ b/viaje/CALENDARIO ROMA definitivo.xlsx
@@ -209,18 +209,6 @@
 Tren Roma - Florencia 14:40-16:17</t>
   </si>
   <si>
-    <t xml:space="preserve">Cruzar rio Tiber: (Por Ponte Sisto)
-Via de la Lungaretta (principal)
-Callejear por Vicolo del Cinque y Via del Moro
-El corazón del barrio: Piazza di Santa María 
-Basílica de Santa María (entrada gratuita)
-Basílica de Santa Cecilia (calma)
-Cruzar río por Isla Tiberina.
-Isola Tiberina (30min)
-Coger tranvía linea 8 desde Belli hacia plaza Venezia 
-</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Siena (Sin prisa):
 </t>
@@ -369,121 +357,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Fase 2 — Zona Imperial (paseo por Via dei Fori Imperiali)
-Via dei Fori Imperiali
-Foro de Augusto
-Foro de Trajano
-Columna de Trajano
-Mercado de Trajano (24 min) (15:30-16:30)
-Altare della Patria (15:30-16:30)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Panteon visita a las 17:00 (22m)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Campidoglio - VISTAS (Plaza diseñada por Miguel Ángel, Vista espectacular 18:30 atardecer) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">del Foro desde el mirador trasero)
-Plaza Navona (27 min)
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Metro linea A </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(estación Repúbblica/Teatro del Opera - Ottaviano) (dirección Battistini)</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Visita Vaticano 10:00 (Viale Giulio Cesare, 229 (Cine Giulio)) (58min)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Castel Sant Angelo (visto desde abajo, caminando al lado del río Tiber).
-Campo de Fiori (28 min) (mercado matutino) ( comer "schiacciata" o pizza al corte) (no mucho tiiempo)
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">Tarde camino al norte: Cruza el centro histórico en dirección norte hacia la zona de San Marcos. Pasarás cerca del Palacio Medici Riccardi y de la Basílica de San Lorenzo, lo que te permite admirar la evolución de la arquitectura renacentista en un paseo muy corto.
 </t>
     </r>
@@ -576,42 +449,160 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Ducha en hotel Caravagio, situado en Via Palermo 75
+    <t>Ducha en hotel Caravagio, situado en Via Palermo 75
 PASEO TRANQUILO: 
 Palazzo delle Esposizioni (3min)
 Giardino di Sant'Andrea al Quirinale (9min)
 Palacio y Plaza del Quirinale (10min)
-Piazza della Pilotta (15min)
 Fontana di Trevi (13-15min)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Plaza de España (17min) (puesta sol escalinata)  (subir sólo hasta la terraza intermedia (gratuita).</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
 Via del Corso (19 min)
-Piazza di San Marcello (18 min)
 Iglesia de San Ignacio de Loyola (19min)
+Piazza de SAn Marcelo
 Plaza de Venecia (17min)
+Plaza de Campidoglio (puesta de sol)
 Hotel Caravaggio (0 min)
 CENA/DESCANSO</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Fase 2 — Zona Imperial (paseo por Via dei Fori Imperiali)
+Via dei Fori Imperiali
+Foro de Augusto
+Foro de Trajano
+Columna de Trajano
+Mercado de Trajano (24 min) (15:30-16:30)
+Altare della Patria (15:30-16:30)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Panteon visita a las 17:00 (22m)
+Plaza Novona</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Campidoglio - VISTAS (Plaza diseñada por Miguel Ángel, Vista espectacular 18:30 atardecer) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">del Foro desde el mirador trasero)
+Plaza Navona (27 min)
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Metro linea A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(estación Repúbblica/Teatro del Opera - Ottaviano) (dirección Battistini)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Visita Vaticano 10:00 (Viale Giulio Cesare, 229 (Cine Giulio)) (58min)
+Después de visita
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Zona del Vaticano → Tíber
+Plaza de San Pedro
+Via della Conciliazione
+Castel Sant'Angelo
+Tíber
+Ponte Sant'Angelo
+🛍️ Camino hacia Plaza de España
+Via di Monte Brianzo
+Via Condotti
+Plaza de España
+Fontana della Barcaccia
+Metro de Roma (acceso con ascensor en la estación de Spagna)
+🏙️ Eje centro histórico
+Via del Babuino
+Plaza del Popolo
+Via del Corso
+Campo de' Fiori
+🌉 Trastevere y regreso por el río
+Ponte Sisto
+Trastevere
+Basílica de Santa María en Trastevere
+Basílica de Santa Cecilia en Trastevere
+Isla Tiberina
+VUELTA EN TRANVIA</t>
     </r>
   </si>
 </sst>
@@ -1015,7 +1006,7 @@
     <col min="1" max="1" width="11.5546875" style="4"/>
     <col min="2" max="2" width="43.88671875" customWidth="1"/>
     <col min="3" max="3" width="61.77734375" customWidth="1"/>
-    <col min="4" max="4" width="39.44140625" customWidth="1"/>
+    <col min="4" max="4" width="61.88671875" customWidth="1"/>
     <col min="5" max="5" width="50.44140625" customWidth="1"/>
     <col min="6" max="6" width="42.109375" customWidth="1"/>
     <col min="7" max="7" width="39.109375" customWidth="1"/>
@@ -1046,7 +1037,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="242.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="409.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1054,19 +1045,19 @@
         <v>9</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>14</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>10</v>
@@ -1077,19 +1068,19 @@
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>12</v>
